--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1492,6 +1492,1594 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132335166</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96526</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>210</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet, öster om norra delen, vid Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>348580</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6519243</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Murken granstam.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132335165</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96526</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>210</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet, ca 80 m NO om tjärnets norra ände, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>348522</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6519365</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Murken låga, obestämt trädslag.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132335807</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96398</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet, 60 m O nordänden, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>348516</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6519293</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>På ek.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132336006</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101296</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>348550</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6519223</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132335439</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96430</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>348505</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6519139</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Grov, murken granlåga.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132335808</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101296</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>348481</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6519286</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132335525</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>348462</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6519162</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132336196</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101296</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>348529</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6519171</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132336000</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96409</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>348539</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6519214</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132335150</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96526</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>210</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>348505</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6519139</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Grov, murken granlåga.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132335809</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96398</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet, 75 m NV nordänden, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>348379</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6519389</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>På ek och berg.</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132335997</v>
+      </c>
+      <c r="B20" t="n">
+        <v>95916</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2362</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blek stjärnmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Mnium stellare</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>348539</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6519214</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132335167</v>
+      </c>
+      <c r="B21" t="n">
+        <v>96526</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>210</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet, öster om norra delen, vid Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>348595</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6519199</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Murken granstuppe.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132335999</v>
+      </c>
+      <c r="B22" t="n">
+        <v>96203</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>348539</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6519214</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132336478</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101296</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>348493</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6519126</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1930,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132335439</v>
+        <v>132335808</v>
       </c>
       <c r="B13" t="n">
-        <v>96430</v>
+        <v>101296</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,34 +1941,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>348505</v>
+        <v>348481</v>
       </c>
       <c r="R13" t="n">
-        <v>6519139</v>
+        <v>6519286</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,16 +2011,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Grov, murken granlåga.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2037,10 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132335808</v>
+        <v>132335439</v>
       </c>
       <c r="B14" t="n">
-        <v>101296</v>
+        <v>96430</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,34 +2038,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>348481</v>
+        <v>348505</v>
       </c>
       <c r="R14" t="n">
-        <v>6519286</v>
+        <v>6519139</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,6 +2108,16 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Grov, murken granlåga.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132336196</v>
+        <v>132336000</v>
       </c>
       <c r="B16" t="n">
-        <v>101296</v>
+        <v>96409</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,21 +2254,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>348529</v>
+        <v>348539</v>
       </c>
       <c r="R16" t="n">
-        <v>6519171</v>
+        <v>6519214</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132336000</v>
+        <v>132336196</v>
       </c>
       <c r="B17" t="n">
-        <v>96409</v>
+        <v>101296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>348539</v>
+        <v>348529</v>
       </c>
       <c r="R17" t="n">
-        <v>6519214</v>
+        <v>6519171</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1497,7 +1497,7 @@
         <v>132335166</v>
       </c>
       <c r="B9" t="n">
-        <v>96526</v>
+        <v>96531</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132335165</v>
       </c>
       <c r="B10" t="n">
-        <v>96526</v>
+        <v>96531</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>132335807</v>
       </c>
       <c r="B11" t="n">
-        <v>96398</v>
+        <v>96403</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>132336006</v>
       </c>
       <c r="B12" t="n">
-        <v>101296</v>
+        <v>101301</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132335808</v>
+        <v>132335439</v>
       </c>
       <c r="B13" t="n">
-        <v>101296</v>
+        <v>96435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,34 +1941,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>348481</v>
+        <v>348505</v>
       </c>
       <c r="R13" t="n">
-        <v>6519286</v>
+        <v>6519139</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,6 +2011,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Grov, murken granlåga.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2027,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132335439</v>
+        <v>132335808</v>
       </c>
       <c r="B14" t="n">
-        <v>96430</v>
+        <v>101301</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2038,34 +2048,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>348505</v>
+        <v>348481</v>
       </c>
       <c r="R14" t="n">
-        <v>6519139</v>
+        <v>6519286</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2108,16 +2118,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Grov, murken granlåga.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2246,7 +2246,7 @@
         <v>132336000</v>
       </c>
       <c r="B16" t="n">
-        <v>96409</v>
+        <v>96414</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>132336196</v>
       </c>
       <c r="B17" t="n">
-        <v>101296</v>
+        <v>101301</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>132335150</v>
       </c>
       <c r="B18" t="n">
-        <v>96526</v>
+        <v>96531</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>132335809</v>
       </c>
       <c r="B19" t="n">
-        <v>96398</v>
+        <v>96403</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>132335997</v>
       </c>
       <c r="B20" t="n">
-        <v>95916</v>
+        <v>95921</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>132335167</v>
       </c>
       <c r="B21" t="n">
-        <v>96526</v>
+        <v>96531</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>132335999</v>
       </c>
       <c r="B22" t="n">
-        <v>96203</v>
+        <v>96208</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>132336478</v>
       </c>
       <c r="B23" t="n">
-        <v>101296</v>
+        <v>101301</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3079,6 +3079,210 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132397690</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97788</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2604</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Trädporella</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Porella platyphylla</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Pfeiff.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>348539</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6519214</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132397692</v>
+      </c>
+      <c r="B25" t="n">
+        <v>96163</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2676</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grov baronmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Anomodon viticulosus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>348539</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6519214</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1497,7 +1497,7 @@
         <v>132335166</v>
       </c>
       <c r="B9" t="n">
-        <v>96531</v>
+        <v>96534</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132335165</v>
       </c>
       <c r="B10" t="n">
-        <v>96531</v>
+        <v>96534</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>132335807</v>
       </c>
       <c r="B11" t="n">
-        <v>96403</v>
+        <v>96406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>132336006</v>
       </c>
       <c r="B12" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132335808</v>
+        <v>132335439</v>
       </c>
       <c r="B13" t="n">
-        <v>101301</v>
+        <v>96438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,34 +1941,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>348481</v>
+        <v>348505</v>
       </c>
       <c r="R13" t="n">
-        <v>6519286</v>
+        <v>6519139</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,6 +2011,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Grov, murken granlåga.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2027,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132335439</v>
+        <v>132335808</v>
       </c>
       <c r="B14" t="n">
-        <v>96435</v>
+        <v>101304</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2038,34 +2048,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>348505</v>
+        <v>348481</v>
       </c>
       <c r="R14" t="n">
-        <v>6519139</v>
+        <v>6519286</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2108,16 +2118,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Grov, murken granlåga.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2246,7 +2246,7 @@
         <v>132336000</v>
       </c>
       <c r="B16" t="n">
-        <v>96414</v>
+        <v>96417</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>132336196</v>
       </c>
       <c r="B17" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2447,10 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132335150</v>
+        <v>132335809</v>
       </c>
       <c r="B18" t="n">
-        <v>96531</v>
+        <v>96406</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2458,43 +2458,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>2671</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, 75 m NV nordänden, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>348505</v>
+        <v>348379</v>
       </c>
       <c r="R18" t="n">
-        <v>6519139</v>
+        <v>6519389</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2538,14 +2529,9 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Grov, murken granlåga.</t>
+          <t>På ek och berg.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2563,10 +2549,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132335809</v>
+        <v>132335150</v>
       </c>
       <c r="B19" t="n">
-        <v>96403</v>
+        <v>96534</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2574,34 +2560,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2671</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, 75 m NV nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>348379</v>
+        <v>348505</v>
       </c>
       <c r="R19" t="n">
-        <v>6519389</v>
+        <v>6519139</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2645,9 +2640,14 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>På ek och berg.</t>
+          <t>Grov, murken granlåga.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2668,7 +2668,7 @@
         <v>132335997</v>
       </c>
       <c r="B20" t="n">
-        <v>95921</v>
+        <v>95924</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>132335167</v>
       </c>
       <c r="B21" t="n">
-        <v>96531</v>
+        <v>96534</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>132335999</v>
       </c>
       <c r="B22" t="n">
-        <v>96208</v>
+        <v>96211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>132336478</v>
       </c>
       <c r="B23" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>132397690</v>
       </c>
       <c r="B24" t="n">
-        <v>97788</v>
+        <v>97791</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>132397692</v>
       </c>
       <c r="B25" t="n">
-        <v>96163</v>
+        <v>96166</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3283,6 +3283,2255 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132446061</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80347</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>348457</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6519520</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132446047</v>
+      </c>
+      <c r="B27" t="n">
+        <v>96406</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>348480</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6519264</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132446046</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>348506</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6519266</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132446045</v>
+      </c>
+      <c r="B29" t="n">
+        <v>96211</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>348545</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6519237</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132446053</v>
+      </c>
+      <c r="B30" t="n">
+        <v>111368</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>348463</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6519366</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132446044</v>
+      </c>
+      <c r="B31" t="n">
+        <v>96417</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>348545</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6519237</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132446059</v>
+      </c>
+      <c r="B32" t="n">
+        <v>96211</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>348464</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6519521</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132446063</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>348439</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6519636</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132446066</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>348507</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6519811</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132446058</v>
+      </c>
+      <c r="B35" t="n">
+        <v>96417</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>348464</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6519509</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132446055</v>
+      </c>
+      <c r="B36" t="n">
+        <v>96406</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>348415</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6519441</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132446050</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>348486</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6519319</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132446043</v>
+      </c>
+      <c r="B38" t="n">
+        <v>96406</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>348552</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6519205</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132446056</v>
+      </c>
+      <c r="B39" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>348430</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6519483</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132446051</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92547</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>348495</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6519363</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132446062</v>
+      </c>
+      <c r="B41" t="n">
+        <v>96406</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>348457</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6519522</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132446065</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>348443</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6519628</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132446054</v>
+      </c>
+      <c r="B43" t="n">
+        <v>96406</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>348384</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6519382</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132446048</v>
+      </c>
+      <c r="B44" t="n">
+        <v>96406</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>348482</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6519312</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132446052</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>348480</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6519355</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132446060</v>
+      </c>
+      <c r="B46" t="n">
+        <v>96166</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2676</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Grov baronmossa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Anomodon viticulosus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>348457</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6519520</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>132446064</v>
+      </c>
+      <c r="B47" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>348443</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6519628</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -4816,10 +4816,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132446062</v>
+        <v>132446065</v>
       </c>
       <c r="B41" t="n">
-        <v>96406</v>
+        <v>4775</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4827,34 +4827,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2671</v>
+        <v>100299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>348457</v>
+        <v>348443</v>
       </c>
       <c r="R41" t="n">
-        <v>6519522</v>
+        <v>6519628</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4897,6 +4902,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4913,10 +4933,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132446065</v>
+        <v>132446062</v>
       </c>
       <c r="B42" t="n">
-        <v>4775</v>
+        <v>96406</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4924,39 +4944,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100299</v>
+        <v>2671</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>348443</v>
+        <v>348457</v>
       </c>
       <c r="R42" t="n">
-        <v>6519628</v>
+        <v>6519522</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4999,21 +5014,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1930,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132335439</v>
+        <v>132335808</v>
       </c>
       <c r="B13" t="n">
-        <v>96438</v>
+        <v>101304</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,34 +1941,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>348505</v>
+        <v>348481</v>
       </c>
       <c r="R13" t="n">
-        <v>6519139</v>
+        <v>6519286</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,16 +2011,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Grov, murken granlåga.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2037,10 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132335808</v>
+        <v>132335439</v>
       </c>
       <c r="B14" t="n">
-        <v>101304</v>
+        <v>96438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,34 +2038,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>348481</v>
+        <v>348505</v>
       </c>
       <c r="R14" t="n">
-        <v>6519286</v>
+        <v>6519139</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,6 +2108,16 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Grov, murken granlåga.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2447,10 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132335809</v>
+        <v>132335150</v>
       </c>
       <c r="B18" t="n">
-        <v>96406</v>
+        <v>96534</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2458,34 +2458,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2671</v>
+        <v>210</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, 75 m NV nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>348379</v>
+        <v>348505</v>
       </c>
       <c r="R18" t="n">
-        <v>6519389</v>
+        <v>6519139</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2529,9 +2538,14 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>På ek och berg.</t>
+          <t>Grov, murken granlåga.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2549,10 +2563,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132335150</v>
+        <v>132335809</v>
       </c>
       <c r="B19" t="n">
-        <v>96534</v>
+        <v>96406</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2560,43 +2574,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>210</v>
+        <v>2671</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, 75 m NV nordänden, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>348505</v>
+        <v>348379</v>
       </c>
       <c r="R19" t="n">
-        <v>6519139</v>
+        <v>6519389</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2640,14 +2645,9 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Grov, murken granlåga.</t>
+          <t>På ek och berg.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -4816,10 +4816,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132446065</v>
+        <v>132446062</v>
       </c>
       <c r="B41" t="n">
-        <v>4775</v>
+        <v>96406</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4827,39 +4827,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100299</v>
+        <v>2671</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>348443</v>
+        <v>348457</v>
       </c>
       <c r="R41" t="n">
-        <v>6519628</v>
+        <v>6519522</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4902,21 +4897,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4933,10 +4913,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132446062</v>
+        <v>132446065</v>
       </c>
       <c r="B42" t="n">
-        <v>96406</v>
+        <v>4775</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4944,34 +4924,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2671</v>
+        <v>100299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>348457</v>
+        <v>348443</v>
       </c>
       <c r="R42" t="n">
-        <v>6519522</v>
+        <v>6519628</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5014,6 +4999,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1930,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132335808</v>
+        <v>132335439</v>
       </c>
       <c r="B13" t="n">
-        <v>101304</v>
+        <v>96438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,34 +1941,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>348481</v>
+        <v>348505</v>
       </c>
       <c r="R13" t="n">
-        <v>6519286</v>
+        <v>6519139</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,6 +2011,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Grov, murken granlåga.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2027,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132335439</v>
+        <v>132335808</v>
       </c>
       <c r="B14" t="n">
-        <v>96438</v>
+        <v>101304</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2038,34 +2048,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>348505</v>
+        <v>348481</v>
       </c>
       <c r="R14" t="n">
-        <v>6519139</v>
+        <v>6519286</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2108,16 +2118,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Grov, murken granlåga.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2447,10 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132335150</v>
+        <v>132335809</v>
       </c>
       <c r="B18" t="n">
-        <v>96534</v>
+        <v>96406</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2458,43 +2458,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>2671</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, 75 m NV nordänden, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>348505</v>
+        <v>348379</v>
       </c>
       <c r="R18" t="n">
-        <v>6519139</v>
+        <v>6519389</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2538,14 +2529,9 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Grov, murken granlåga.</t>
+          <t>På ek och berg.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2563,10 +2549,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132335809</v>
+        <v>132335150</v>
       </c>
       <c r="B19" t="n">
-        <v>96406</v>
+        <v>96534</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2574,34 +2560,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2671</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, 75 m NV nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>348379</v>
+        <v>348505</v>
       </c>
       <c r="R19" t="n">
-        <v>6519389</v>
+        <v>6519139</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2645,9 +2640,14 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>På ek och berg.</t>
+          <t>Grov, murken granlåga.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3480,10 +3480,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132446046</v>
+        <v>132446045</v>
       </c>
       <c r="B28" t="n">
-        <v>101304</v>
+        <v>96211</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,21 +3491,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>2779</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>348506</v>
+        <v>348545</v>
       </c>
       <c r="R28" t="n">
-        <v>6519266</v>
+        <v>6519237</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3577,10 +3577,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132446045</v>
+        <v>132446046</v>
       </c>
       <c r="B29" t="n">
-        <v>96211</v>
+        <v>101304</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3588,21 +3588,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2779</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>348545</v>
+        <v>348506</v>
       </c>
       <c r="R29" t="n">
-        <v>6519237</v>
+        <v>6519266</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132446066</v>
+        <v>132446058</v>
       </c>
       <c r="B34" t="n">
-        <v>5199</v>
+        <v>96417</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4093,39 +4093,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>105930</v>
+        <v>2667</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>348507</v>
+        <v>348464</v>
       </c>
       <c r="R34" t="n">
-        <v>6519811</v>
+        <v>6519509</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4168,21 +4163,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4199,10 +4179,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132446058</v>
+        <v>132446066</v>
       </c>
       <c r="B35" t="n">
-        <v>96417</v>
+        <v>5199</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4210,34 +4190,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2667</v>
+        <v>105930</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>348464</v>
+        <v>348507</v>
       </c>
       <c r="R35" t="n">
-        <v>6519509</v>
+        <v>6519811</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4280,6 +4265,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4587,10 +4587,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132446056</v>
+        <v>132446051</v>
       </c>
       <c r="B39" t="n">
-        <v>8455</v>
+        <v>92547</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4598,39 +4598,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>1339</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>348430</v>
+        <v>348495</v>
       </c>
       <c r="R39" t="n">
-        <v>6519483</v>
+        <v>6519363</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4676,17 +4671,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4704,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132446051</v>
+        <v>132446056</v>
       </c>
       <c r="B40" t="n">
-        <v>92547</v>
+        <v>8455</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4715,34 +4710,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1339</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>348495</v>
+        <v>348430</v>
       </c>
       <c r="R40" t="n">
-        <v>6519363</v>
+        <v>6519483</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4788,17 +4788,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -4816,10 +4816,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132446062</v>
+        <v>132446065</v>
       </c>
       <c r="B41" t="n">
-        <v>96406</v>
+        <v>4775</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4827,34 +4827,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2671</v>
+        <v>100299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>348457</v>
+        <v>348443</v>
       </c>
       <c r="R41" t="n">
-        <v>6519522</v>
+        <v>6519628</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4897,6 +4902,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4913,10 +4933,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132446065</v>
+        <v>132446062</v>
       </c>
       <c r="B42" t="n">
-        <v>4775</v>
+        <v>96406</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4924,39 +4944,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100299</v>
+        <v>2671</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>348443</v>
+        <v>348457</v>
       </c>
       <c r="R42" t="n">
-        <v>6519628</v>
+        <v>6519522</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4999,21 +5014,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5127,10 +5127,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132446048</v>
+        <v>132446064</v>
       </c>
       <c r="B44" t="n">
-        <v>96406</v>
+        <v>5199</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5138,34 +5138,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2671</v>
+        <v>105930</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>348482</v>
+        <v>348443</v>
       </c>
       <c r="R44" t="n">
-        <v>6519312</v>
+        <v>6519628</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5208,6 +5213,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5418,10 +5438,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132446064</v>
+        <v>132446048</v>
       </c>
       <c r="B47" t="n">
-        <v>5199</v>
+        <v>96406</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5429,39 +5449,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>105930</v>
+        <v>2671</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>348443</v>
+        <v>348482</v>
       </c>
       <c r="R47" t="n">
-        <v>6519628</v>
+        <v>6519312</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5504,21 +5519,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -4296,10 +4296,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132446055</v>
+        <v>132446050</v>
       </c>
       <c r="B36" t="n">
-        <v>96406</v>
+        <v>101304</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4307,34 +4307,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>348415</v>
+        <v>348486</v>
       </c>
       <c r="R36" t="n">
-        <v>6519441</v>
+        <v>6519319</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132446050</v>
+        <v>132446055</v>
       </c>
       <c r="B37" t="n">
-        <v>101304</v>
+        <v>96406</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4404,34 +4404,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>348486</v>
+        <v>348415</v>
       </c>
       <c r="R37" t="n">
-        <v>6519319</v>
+        <v>6519441</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>132335166</v>
       </c>
       <c r="B9" t="n">
-        <v>96534</v>
+        <v>96542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132335165</v>
       </c>
       <c r="B10" t="n">
-        <v>96534</v>
+        <v>96542</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>132335807</v>
       </c>
       <c r="B11" t="n">
-        <v>96406</v>
+        <v>96414</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>132336006</v>
       </c>
       <c r="B12" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>132335439</v>
       </c>
       <c r="B13" t="n">
-        <v>96438</v>
+        <v>96446</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>132335808</v>
       </c>
       <c r="B14" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>132335525</v>
       </c>
       <c r="B15" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>132336000</v>
       </c>
       <c r="B16" t="n">
-        <v>96417</v>
+        <v>96425</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>132336196</v>
       </c>
       <c r="B17" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2447,10 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132335809</v>
+        <v>132335150</v>
       </c>
       <c r="B18" t="n">
-        <v>96406</v>
+        <v>96542</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2458,34 +2458,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2671</v>
+        <v>210</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, 75 m NV nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>348379</v>
+        <v>348505</v>
       </c>
       <c r="R18" t="n">
-        <v>6519389</v>
+        <v>6519139</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2529,9 +2538,14 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>På ek och berg.</t>
+          <t>Grov, murken granlåga.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2549,10 +2563,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132335150</v>
+        <v>132335809</v>
       </c>
       <c r="B19" t="n">
-        <v>96534</v>
+        <v>96414</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2560,43 +2574,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>210</v>
+        <v>2671</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, 75 m NV nordänden, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>348505</v>
+        <v>348379</v>
       </c>
       <c r="R19" t="n">
-        <v>6519139</v>
+        <v>6519389</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2640,14 +2645,9 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Grov, murken granlåga.</t>
+          <t>På ek och berg.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2668,7 +2668,7 @@
         <v>132335997</v>
       </c>
       <c r="B20" t="n">
-        <v>95924</v>
+        <v>95932</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>132335167</v>
       </c>
       <c r="B21" t="n">
-        <v>96534</v>
+        <v>96542</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>132335999</v>
       </c>
       <c r="B22" t="n">
-        <v>96211</v>
+        <v>96219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>132336478</v>
       </c>
       <c r="B23" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>132397690</v>
       </c>
       <c r="B24" t="n">
-        <v>97791</v>
+        <v>97799</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>132397692</v>
       </c>
       <c r="B25" t="n">
-        <v>96166</v>
+        <v>96174</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>132446061</v>
       </c>
       <c r="B26" t="n">
-        <v>80347</v>
+        <v>80349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>132446047</v>
       </c>
       <c r="B27" t="n">
-        <v>96406</v>
+        <v>96414</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>132446045</v>
       </c>
       <c r="B28" t="n">
-        <v>96211</v>
+        <v>96219</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>132446046</v>
       </c>
       <c r="B29" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>132446053</v>
       </c>
       <c r="B30" t="n">
-        <v>111368</v>
+        <v>111376</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>132446044</v>
       </c>
       <c r="B31" t="n">
-        <v>96417</v>
+        <v>96425</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>132446059</v>
       </c>
       <c r="B32" t="n">
-        <v>96211</v>
+        <v>96219</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>132446058</v>
       </c>
       <c r="B34" t="n">
-        <v>96417</v>
+        <v>96425</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>132446050</v>
       </c>
       <c r="B36" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>132446055</v>
       </c>
       <c r="B37" t="n">
-        <v>96406</v>
+        <v>96414</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>132446043</v>
       </c>
       <c r="B38" t="n">
-        <v>96406</v>
+        <v>96414</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>132446051</v>
       </c>
       <c r="B39" t="n">
-        <v>92547</v>
+        <v>92553</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>132446062</v>
       </c>
       <c r="B42" t="n">
-        <v>96406</v>
+        <v>96414</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>132446054</v>
       </c>
       <c r="B43" t="n">
-        <v>96406</v>
+        <v>96414</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5127,10 +5127,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132446064</v>
+        <v>132446060</v>
       </c>
       <c r="B44" t="n">
-        <v>5199</v>
+        <v>96174</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5138,39 +5138,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>105930</v>
+        <v>2676</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>348443</v>
+        <v>348457</v>
       </c>
       <c r="R44" t="n">
-        <v>6519628</v>
+        <v>6519520</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5213,21 +5208,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5244,10 +5224,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132446052</v>
+        <v>132446048</v>
       </c>
       <c r="B45" t="n">
-        <v>101304</v>
+        <v>96414</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5255,34 +5235,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>348480</v>
+        <v>348482</v>
       </c>
       <c r="R45" t="n">
-        <v>6519355</v>
+        <v>6519312</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5341,10 +5321,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132446060</v>
+        <v>132446064</v>
       </c>
       <c r="B46" t="n">
-        <v>96166</v>
+        <v>5199</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5352,34 +5332,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2676</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>348457</v>
+        <v>348443</v>
       </c>
       <c r="R46" t="n">
-        <v>6519520</v>
+        <v>6519628</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5422,6 +5407,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5438,10 +5438,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132446048</v>
+        <v>132446052</v>
       </c>
       <c r="B47" t="n">
-        <v>96406</v>
+        <v>101312</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5449,34 +5449,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>348482</v>
+        <v>348480</v>
       </c>
       <c r="R47" t="n">
-        <v>6519312</v>
+        <v>6519355</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1930,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132335439</v>
+        <v>132335808</v>
       </c>
       <c r="B13" t="n">
-        <v>96446</v>
+        <v>101312</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,34 +1941,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>348505</v>
+        <v>348481</v>
       </c>
       <c r="R13" t="n">
-        <v>6519139</v>
+        <v>6519286</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,16 +2011,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Grov, murken granlåga.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2037,10 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132335808</v>
+        <v>132335439</v>
       </c>
       <c r="B14" t="n">
-        <v>101312</v>
+        <v>96446</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,34 +2038,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>348481</v>
+        <v>348505</v>
       </c>
       <c r="R14" t="n">
-        <v>6519286</v>
+        <v>6519139</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,6 +2108,16 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Grov, murken granlåga.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132336000</v>
+        <v>132336196</v>
       </c>
       <c r="B16" t="n">
-        <v>96425</v>
+        <v>101312</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,21 +2254,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>348539</v>
+        <v>348529</v>
       </c>
       <c r="R16" t="n">
-        <v>6519214</v>
+        <v>6519171</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132336196</v>
+        <v>132336000</v>
       </c>
       <c r="B17" t="n">
-        <v>101312</v>
+        <v>96425</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>348529</v>
+        <v>348539</v>
       </c>
       <c r="R17" t="n">
-        <v>6519171</v>
+        <v>6519214</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3480,10 +3480,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132446045</v>
+        <v>132446046</v>
       </c>
       <c r="B28" t="n">
-        <v>96219</v>
+        <v>101312</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,21 +3491,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2779</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>348545</v>
+        <v>348506</v>
       </c>
       <c r="R28" t="n">
-        <v>6519237</v>
+        <v>6519266</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3577,10 +3577,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132446046</v>
+        <v>132446045</v>
       </c>
       <c r="B29" t="n">
-        <v>101312</v>
+        <v>96219</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3588,21 +3588,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>2779</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>348506</v>
+        <v>348545</v>
       </c>
       <c r="R29" t="n">
-        <v>6519266</v>
+        <v>6519237</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132446058</v>
+        <v>132446066</v>
       </c>
       <c r="B34" t="n">
-        <v>96425</v>
+        <v>5199</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4093,34 +4093,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2667</v>
+        <v>105930</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>348464</v>
+        <v>348507</v>
       </c>
       <c r="R34" t="n">
-        <v>6519509</v>
+        <v>6519811</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4163,6 +4168,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4179,10 +4199,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132446066</v>
+        <v>132446058</v>
       </c>
       <c r="B35" t="n">
-        <v>5199</v>
+        <v>96425</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4190,39 +4210,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
+        <v>2667</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>348507</v>
+        <v>348464</v>
       </c>
       <c r="R35" t="n">
-        <v>6519811</v>
+        <v>6519509</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4265,21 +4280,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4296,10 +4296,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132446050</v>
+        <v>132446055</v>
       </c>
       <c r="B36" t="n">
-        <v>101312</v>
+        <v>96414</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4307,34 +4307,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>348486</v>
+        <v>348415</v>
       </c>
       <c r="R36" t="n">
-        <v>6519319</v>
+        <v>6519441</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132446055</v>
+        <v>132446050</v>
       </c>
       <c r="B37" t="n">
-        <v>96414</v>
+        <v>101312</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4404,34 +4404,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>348415</v>
+        <v>348486</v>
       </c>
       <c r="R37" t="n">
-        <v>6519441</v>
+        <v>6519319</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4816,10 +4816,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132446065</v>
+        <v>132446062</v>
       </c>
       <c r="B41" t="n">
-        <v>4775</v>
+        <v>96414</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4827,39 +4827,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100299</v>
+        <v>2671</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>348443</v>
+        <v>348457</v>
       </c>
       <c r="R41" t="n">
-        <v>6519628</v>
+        <v>6519522</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4902,21 +4897,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4933,10 +4913,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132446062</v>
+        <v>132446065</v>
       </c>
       <c r="B42" t="n">
-        <v>96414</v>
+        <v>4775</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4944,34 +4924,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2671</v>
+        <v>100299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>348457</v>
+        <v>348443</v>
       </c>
       <c r="R42" t="n">
-        <v>6519522</v>
+        <v>6519628</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5014,6 +4999,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>132335166</v>
       </c>
       <c r="B9" t="n">
-        <v>96542</v>
+        <v>96552</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132335165</v>
       </c>
       <c r="B10" t="n">
-        <v>96542</v>
+        <v>96552</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>132335807</v>
       </c>
       <c r="B11" t="n">
-        <v>96414</v>
+        <v>96424</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>132336006</v>
       </c>
       <c r="B12" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>132335808</v>
       </c>
       <c r="B13" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>132335439</v>
       </c>
       <c r="B14" t="n">
-        <v>96446</v>
+        <v>96456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>132335525</v>
       </c>
       <c r="B15" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132336196</v>
+        <v>132336000</v>
       </c>
       <c r="B16" t="n">
-        <v>101312</v>
+        <v>96435</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,21 +2254,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>348529</v>
+        <v>348539</v>
       </c>
       <c r="R16" t="n">
-        <v>6519171</v>
+        <v>6519214</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132336000</v>
+        <v>132336196</v>
       </c>
       <c r="B17" t="n">
-        <v>96425</v>
+        <v>101323</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>348539</v>
+        <v>348529</v>
       </c>
       <c r="R17" t="n">
-        <v>6519214</v>
+        <v>6519171</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2447,10 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132335150</v>
+        <v>132335809</v>
       </c>
       <c r="B18" t="n">
-        <v>96542</v>
+        <v>96424</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2458,43 +2458,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>2671</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, 75 m NV nordänden, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>348505</v>
+        <v>348379</v>
       </c>
       <c r="R18" t="n">
-        <v>6519139</v>
+        <v>6519389</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2538,14 +2529,9 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Grov, murken granlåga.</t>
+          <t>På ek och berg.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2563,10 +2549,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132335809</v>
+        <v>132335150</v>
       </c>
       <c r="B19" t="n">
-        <v>96414</v>
+        <v>96552</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2574,34 +2560,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2671</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, 75 m NV nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>348379</v>
+        <v>348505</v>
       </c>
       <c r="R19" t="n">
-        <v>6519389</v>
+        <v>6519139</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2645,9 +2640,14 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>På ek och berg.</t>
+          <t>Grov, murken granlåga.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2668,7 +2668,7 @@
         <v>132335997</v>
       </c>
       <c r="B20" t="n">
-        <v>95932</v>
+        <v>95942</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>132335167</v>
       </c>
       <c r="B21" t="n">
-        <v>96542</v>
+        <v>96552</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>132335999</v>
       </c>
       <c r="B22" t="n">
-        <v>96219</v>
+        <v>96229</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>132336478</v>
       </c>
       <c r="B23" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>132397690</v>
       </c>
       <c r="B24" t="n">
-        <v>97799</v>
+        <v>97809</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>132397692</v>
       </c>
       <c r="B25" t="n">
-        <v>96174</v>
+        <v>96184</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>132446061</v>
       </c>
       <c r="B26" t="n">
-        <v>80349</v>
+        <v>80357</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>132446047</v>
       </c>
       <c r="B27" t="n">
-        <v>96414</v>
+        <v>96424</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,10 +3480,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132446046</v>
+        <v>132446045</v>
       </c>
       <c r="B28" t="n">
-        <v>101312</v>
+        <v>96229</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,21 +3491,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>2779</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>348506</v>
+        <v>348545</v>
       </c>
       <c r="R28" t="n">
-        <v>6519266</v>
+        <v>6519237</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3577,10 +3577,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132446045</v>
+        <v>132446046</v>
       </c>
       <c r="B29" t="n">
-        <v>96219</v>
+        <v>101323</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3588,21 +3588,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2779</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>348545</v>
+        <v>348506</v>
       </c>
       <c r="R29" t="n">
-        <v>6519237</v>
+        <v>6519266</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3677,7 +3677,7 @@
         <v>132446053</v>
       </c>
       <c r="B30" t="n">
-        <v>111376</v>
+        <v>111387</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>132446044</v>
       </c>
       <c r="B31" t="n">
-        <v>96425</v>
+        <v>96435</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>132446059</v>
       </c>
       <c r="B32" t="n">
-        <v>96219</v>
+        <v>96229</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132446066</v>
+        <v>132446058</v>
       </c>
       <c r="B34" t="n">
-        <v>5199</v>
+        <v>96435</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4093,39 +4093,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>105930</v>
+        <v>2667</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>348507</v>
+        <v>348464</v>
       </c>
       <c r="R34" t="n">
-        <v>6519811</v>
+        <v>6519509</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4168,21 +4163,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4199,10 +4179,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132446058</v>
+        <v>132446066</v>
       </c>
       <c r="B35" t="n">
-        <v>96425</v>
+        <v>5199</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4210,34 +4190,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2667</v>
+        <v>105930</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>348464</v>
+        <v>348507</v>
       </c>
       <c r="R35" t="n">
-        <v>6519509</v>
+        <v>6519811</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4280,6 +4265,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4299,7 +4299,7 @@
         <v>132446055</v>
       </c>
       <c r="B36" t="n">
-        <v>96414</v>
+        <v>96424</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>132446050</v>
       </c>
       <c r="B37" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>132446043</v>
       </c>
       <c r="B38" t="n">
-        <v>96414</v>
+        <v>96424</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>132446051</v>
       </c>
       <c r="B39" t="n">
-        <v>92553</v>
+        <v>92563</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>132446062</v>
       </c>
       <c r="B41" t="n">
-        <v>96414</v>
+        <v>96424</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>132446054</v>
       </c>
       <c r="B43" t="n">
-        <v>96414</v>
+        <v>96424</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5127,10 +5127,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132446060</v>
+        <v>132446052</v>
       </c>
       <c r="B44" t="n">
-        <v>96174</v>
+        <v>101323</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5138,34 +5138,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2676</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>348457</v>
+        <v>348480</v>
       </c>
       <c r="R44" t="n">
-        <v>6519520</v>
+        <v>6519355</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5224,10 +5224,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132446048</v>
+        <v>132446064</v>
       </c>
       <c r="B45" t="n">
-        <v>96414</v>
+        <v>5199</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5235,34 +5235,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2671</v>
+        <v>105930</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>348482</v>
+        <v>348443</v>
       </c>
       <c r="R45" t="n">
-        <v>6519312</v>
+        <v>6519628</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5305,6 +5310,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5321,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132446064</v>
+        <v>132446048</v>
       </c>
       <c r="B46" t="n">
-        <v>5199</v>
+        <v>96424</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5332,39 +5352,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>2671</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>348443</v>
+        <v>348482</v>
       </c>
       <c r="R46" t="n">
-        <v>6519628</v>
+        <v>6519312</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5407,21 +5422,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5438,10 +5438,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132446052</v>
+        <v>132446060</v>
       </c>
       <c r="B47" t="n">
-        <v>101312</v>
+        <v>96184</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5449,34 +5449,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>2676</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>348480</v>
+        <v>348457</v>
       </c>
       <c r="R47" t="n">
-        <v>6519355</v>
+        <v>6519520</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>132335166</v>
       </c>
       <c r="B9" t="n">
-        <v>96552</v>
+        <v>96553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132335165</v>
       </c>
       <c r="B10" t="n">
-        <v>96552</v>
+        <v>96553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>132335807</v>
       </c>
       <c r="B11" t="n">
-        <v>96424</v>
+        <v>96425</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>132336006</v>
       </c>
       <c r="B12" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132335808</v>
+        <v>132335439</v>
       </c>
       <c r="B13" t="n">
-        <v>101323</v>
+        <v>96457</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,34 +1941,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>348481</v>
+        <v>348505</v>
       </c>
       <c r="R13" t="n">
-        <v>6519286</v>
+        <v>6519139</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,6 +2011,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Grov, murken granlåga.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2027,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132335439</v>
+        <v>132335808</v>
       </c>
       <c r="B14" t="n">
-        <v>96456</v>
+        <v>101324</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2038,34 +2048,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>348505</v>
+        <v>348481</v>
       </c>
       <c r="R14" t="n">
-        <v>6519139</v>
+        <v>6519286</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2108,16 +2118,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Grov, murken granlåga.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2246,7 +2246,7 @@
         <v>132336000</v>
       </c>
       <c r="B16" t="n">
-        <v>96435</v>
+        <v>96436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>132336196</v>
       </c>
       <c r="B17" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>132335809</v>
       </c>
       <c r="B18" t="n">
-        <v>96424</v>
+        <v>96425</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>132335150</v>
       </c>
       <c r="B19" t="n">
-        <v>96552</v>
+        <v>96553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>132335997</v>
       </c>
       <c r="B20" t="n">
-        <v>95942</v>
+        <v>95943</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>132335167</v>
       </c>
       <c r="B21" t="n">
-        <v>96552</v>
+        <v>96553</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>132335999</v>
       </c>
       <c r="B22" t="n">
-        <v>96229</v>
+        <v>96230</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>132336478</v>
       </c>
       <c r="B23" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>132397690</v>
       </c>
       <c r="B24" t="n">
-        <v>97809</v>
+        <v>97810</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>132397692</v>
       </c>
       <c r="B25" t="n">
-        <v>96184</v>
+        <v>96185</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>132446047</v>
       </c>
       <c r="B27" t="n">
-        <v>96424</v>
+        <v>96425</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>132446045</v>
       </c>
       <c r="B28" t="n">
-        <v>96229</v>
+        <v>96230</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>132446046</v>
       </c>
       <c r="B29" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>132446053</v>
       </c>
       <c r="B30" t="n">
-        <v>111387</v>
+        <v>111388</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>132446044</v>
       </c>
       <c r="B31" t="n">
-        <v>96435</v>
+        <v>96436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>132446059</v>
       </c>
       <c r="B32" t="n">
-        <v>96229</v>
+        <v>96230</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>132446058</v>
       </c>
       <c r="B34" t="n">
-        <v>96435</v>
+        <v>96436</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>132446055</v>
       </c>
       <c r="B36" t="n">
-        <v>96424</v>
+        <v>96425</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>132446050</v>
       </c>
       <c r="B37" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>132446043</v>
       </c>
       <c r="B38" t="n">
-        <v>96424</v>
+        <v>96425</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>132446051</v>
       </c>
       <c r="B39" t="n">
-        <v>92563</v>
+        <v>92564</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>132446062</v>
       </c>
       <c r="B41" t="n">
-        <v>96424</v>
+        <v>96425</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>132446054</v>
       </c>
       <c r="B43" t="n">
-        <v>96424</v>
+        <v>96425</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>132446052</v>
       </c>
       <c r="B44" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5224,10 +5224,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132446064</v>
+        <v>132446048</v>
       </c>
       <c r="B45" t="n">
-        <v>5199</v>
+        <v>96425</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5235,39 +5235,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>105930</v>
+        <v>2671</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>348443</v>
+        <v>348482</v>
       </c>
       <c r="R45" t="n">
-        <v>6519628</v>
+        <v>6519312</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5310,21 +5305,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5341,10 +5321,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132446048</v>
+        <v>132446060</v>
       </c>
       <c r="B46" t="n">
-        <v>96424</v>
+        <v>96185</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5352,34 +5332,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2671</v>
+        <v>2676</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>348482</v>
+        <v>348457</v>
       </c>
       <c r="R46" t="n">
-        <v>6519312</v>
+        <v>6519520</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5438,10 +5418,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132446060</v>
+        <v>132446064</v>
       </c>
       <c r="B47" t="n">
-        <v>96184</v>
+        <v>5199</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5449,34 +5429,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2676</v>
+        <v>105930</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>348457</v>
+        <v>348443</v>
       </c>
       <c r="R47" t="n">
-        <v>6519520</v>
+        <v>6519628</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5519,6 +5504,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>132335166</v>
       </c>
       <c r="B9" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>132335165</v>
       </c>
       <c r="B10" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>132335807</v>
       </c>
       <c r="B11" t="n">
-        <v>96425</v>
+        <v>96426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>132336006</v>
       </c>
       <c r="B12" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>132335439</v>
       </c>
       <c r="B13" t="n">
-        <v>96457</v>
+        <v>96458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>132335808</v>
       </c>
       <c r="B14" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132336000</v>
+        <v>132336196</v>
       </c>
       <c r="B16" t="n">
-        <v>96436</v>
+        <v>101325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,21 +2254,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>348539</v>
+        <v>348529</v>
       </c>
       <c r="R16" t="n">
-        <v>6519214</v>
+        <v>6519171</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132336196</v>
+        <v>132336000</v>
       </c>
       <c r="B17" t="n">
-        <v>101324</v>
+        <v>96437</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>348529</v>
+        <v>348539</v>
       </c>
       <c r="R17" t="n">
-        <v>6519171</v>
+        <v>6519214</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
         <v>132335809</v>
       </c>
       <c r="B18" t="n">
-        <v>96425</v>
+        <v>96426</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>132335150</v>
       </c>
       <c r="B19" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>132335997</v>
       </c>
       <c r="B20" t="n">
-        <v>95943</v>
+        <v>95944</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>132335167</v>
       </c>
       <c r="B21" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>132335999</v>
       </c>
       <c r="B22" t="n">
-        <v>96230</v>
+        <v>96231</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>132336478</v>
       </c>
       <c r="B23" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>132397690</v>
       </c>
       <c r="B24" t="n">
-        <v>97810</v>
+        <v>97811</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>132397692</v>
       </c>
       <c r="B25" t="n">
-        <v>96185</v>
+        <v>96186</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>132446047</v>
       </c>
       <c r="B27" t="n">
-        <v>96425</v>
+        <v>96426</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>132446045</v>
       </c>
       <c r="B28" t="n">
-        <v>96230</v>
+        <v>96231</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>132446046</v>
       </c>
       <c r="B29" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>132446053</v>
       </c>
       <c r="B30" t="n">
-        <v>111388</v>
+        <v>111389</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>132446044</v>
       </c>
       <c r="B31" t="n">
-        <v>96436</v>
+        <v>96437</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>132446059</v>
       </c>
       <c r="B32" t="n">
-        <v>96230</v>
+        <v>96231</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>132446058</v>
       </c>
       <c r="B34" t="n">
-        <v>96436</v>
+        <v>96437</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>132446055</v>
       </c>
       <c r="B36" t="n">
-        <v>96425</v>
+        <v>96426</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>132446050</v>
       </c>
       <c r="B37" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>132446043</v>
       </c>
       <c r="B38" t="n">
-        <v>96425</v>
+        <v>96426</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>132446062</v>
       </c>
       <c r="B41" t="n">
-        <v>96425</v>
+        <v>96426</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>132446054</v>
       </c>
       <c r="B43" t="n">
-        <v>96425</v>
+        <v>96426</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5127,10 +5127,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132446052</v>
+        <v>132446060</v>
       </c>
       <c r="B44" t="n">
-        <v>101324</v>
+        <v>96186</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5138,34 +5138,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>2676</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>348480</v>
+        <v>348457</v>
       </c>
       <c r="R44" t="n">
-        <v>6519355</v>
+        <v>6519520</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5227,7 +5227,7 @@
         <v>132446048</v>
       </c>
       <c r="B45" t="n">
-        <v>96425</v>
+        <v>96426</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5321,10 +5321,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132446060</v>
+        <v>132446064</v>
       </c>
       <c r="B46" t="n">
-        <v>96185</v>
+        <v>5199</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5332,34 +5332,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2676</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>348457</v>
+        <v>348443</v>
       </c>
       <c r="R46" t="n">
-        <v>6519520</v>
+        <v>6519628</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5402,6 +5407,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5418,10 +5438,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132446064</v>
+        <v>132446052</v>
       </c>
       <c r="B47" t="n">
-        <v>5199</v>
+        <v>101325</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5429,39 +5449,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>348443</v>
+        <v>348480</v>
       </c>
       <c r="R47" t="n">
-        <v>6519628</v>
+        <v>6519355</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5504,21 +5519,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132336196</v>
+        <v>132336000</v>
       </c>
       <c r="B16" t="n">
-        <v>101325</v>
+        <v>96437</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,21 +2254,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>348529</v>
+        <v>348539</v>
       </c>
       <c r="R16" t="n">
-        <v>6519171</v>
+        <v>6519214</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132336000</v>
+        <v>132336196</v>
       </c>
       <c r="B17" t="n">
-        <v>96437</v>
+        <v>101325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2667</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>348539</v>
+        <v>348529</v>
       </c>
       <c r="R17" t="n">
-        <v>6519214</v>
+        <v>6519171</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -5127,10 +5127,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132446060</v>
+        <v>132446064</v>
       </c>
       <c r="B44" t="n">
-        <v>96186</v>
+        <v>5199</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5138,34 +5138,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2676</v>
+        <v>105930</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>348457</v>
+        <v>348443</v>
       </c>
       <c r="R44" t="n">
-        <v>6519520</v>
+        <v>6519628</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5208,6 +5213,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5224,10 +5244,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132446048</v>
+        <v>132446060</v>
       </c>
       <c r="B45" t="n">
-        <v>96426</v>
+        <v>96186</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5235,34 +5255,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2671</v>
+        <v>2676</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>348482</v>
+        <v>348457</v>
       </c>
       <c r="R45" t="n">
-        <v>6519312</v>
+        <v>6519520</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5321,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132446064</v>
+        <v>132446048</v>
       </c>
       <c r="B46" t="n">
-        <v>5199</v>
+        <v>96426</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5332,39 +5352,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>2671</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>348443</v>
+        <v>348482</v>
       </c>
       <c r="R46" t="n">
-        <v>6519628</v>
+        <v>6519312</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5407,21 +5422,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336454</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446067</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335150</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335165</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1224,6 +1249,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335166</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335167</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1452,6 +1487,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446051</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1554,6 +1594,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335997</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1656,6 +1701,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132397690</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1758,6 +1808,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336000</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1855,6 +1910,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446044</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1952,6 +2012,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446058</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2054,6 +2119,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335807</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,6 +2226,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335809</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2253,6 +2328,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446043</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2350,6 +2430,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446047</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2447,6 +2532,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446048</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2544,6 +2634,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446054</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2641,6 +2736,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446055</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2738,6 +2838,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446062</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2840,6 +2945,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132397692</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2937,6 +3047,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446060</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3039,6 +3154,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335999</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3136,6 +3256,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446045</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3233,6 +3358,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446059</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3340,6 +3470,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335439</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3449,6 +3584,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335525</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3566,6 +3706,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446065</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3683,6 +3828,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446063</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3800,6 +3950,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446064</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3917,6 +4072,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446066</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4034,6 +4194,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446029</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4151,6 +4316,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446056</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4248,6 +4418,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446053</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4360,6 +4535,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121791871</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4472,6 +4652,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121792063</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4584,6 +4769,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121792253</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4696,6 +4886,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121792318</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4808,6 +5003,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121792399</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4920,6 +5120,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121792568</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5032,6 +5237,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121792607</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5129,6 +5339,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132335808</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5231,6 +5446,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336006</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5333,6 +5553,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336196</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5430,6 +5655,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336478</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5527,6 +5757,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446046</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5624,6 +5859,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446050</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5721,6 +5961,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446052</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5823,6 +6068,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336005</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5920,8 +6170,65 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446061</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ51"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2020,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132335807</v>
+        <v>136097908</v>
       </c>
       <c r="B14" t="n">
-        <v>96501</v>
+        <v>96607</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,37 +2031,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, 60 m O nordänden, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>348516</v>
       </c>
       <c r="R14" t="n">
-        <v>6519293</v>
+        <v>6519369</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2085,12 +2085,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2102,32 +2102,42 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>På ek.</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335807</t>
+          <t>https://artportalen.se/Sighting/136097908</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132335809</v>
+        <v>132335807</v>
       </c>
       <c r="B15" t="n">
         <v>96501</v>
@@ -2158,14 +2168,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, 75 m NV nordänden, Dls</t>
+          <t>Vandringstjärnet, 60 m O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>348379</v>
+        <v>348516</v>
       </c>
       <c r="R15" t="n">
-        <v>6519389</v>
+        <v>6519293</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,7 +2221,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>På ek och berg.</t>
+          <t>På ek.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2228,13 +2238,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335809</t>
+          <t>https://artportalen.se/Sighting/132335807</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132446043</v>
+        <v>132335809</v>
       </c>
       <c r="B16" t="n">
         <v>96501</v>
@@ -2265,17 +2275,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, 75 m NV nordänden, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>348552</v>
+        <v>348379</v>
       </c>
       <c r="R16" t="n">
-        <v>6519205</v>
+        <v>6519389</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2299,12 +2309,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,28 +2325,33 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>På ek och berg.</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446043</t>
+          <t>https://artportalen.se/Sighting/132335809</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132446047</v>
+        <v>132446043</v>
       </c>
       <c r="B17" t="n">
         <v>96501</v>
@@ -2371,10 +2386,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>348480</v>
+        <v>348552</v>
       </c>
       <c r="R17" t="n">
-        <v>6519264</v>
+        <v>6519205</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2432,13 +2447,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446047</t>
+          <t>https://artportalen.se/Sighting/132446043</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132446048</v>
+        <v>132446047</v>
       </c>
       <c r="B18" t="n">
         <v>96501</v>
@@ -2473,10 +2488,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>348482</v>
+        <v>348480</v>
       </c>
       <c r="R18" t="n">
-        <v>6519312</v>
+        <v>6519264</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2534,13 +2549,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446048</t>
+          <t>https://artportalen.se/Sighting/132446047</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132446054</v>
+        <v>132446048</v>
       </c>
       <c r="B19" t="n">
         <v>96501</v>
@@ -2571,14 +2586,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>348384</v>
+        <v>348482</v>
       </c>
       <c r="R19" t="n">
-        <v>6519382</v>
+        <v>6519312</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2636,13 +2651,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446054</t>
+          <t>https://artportalen.se/Sighting/132446048</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132446055</v>
+        <v>132446054</v>
       </c>
       <c r="B20" t="n">
         <v>96501</v>
@@ -2677,10 +2692,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>348415</v>
+        <v>348384</v>
       </c>
       <c r="R20" t="n">
-        <v>6519441</v>
+        <v>6519382</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2738,13 +2753,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446055</t>
+          <t>https://artportalen.se/Sighting/132446054</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132446062</v>
+        <v>132446055</v>
       </c>
       <c r="B21" t="n">
         <v>96501</v>
@@ -2775,14 +2790,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>348457</v>
+        <v>348415</v>
       </c>
       <c r="R21" t="n">
-        <v>6519522</v>
+        <v>6519441</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2840,16 +2855,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446062</t>
+          <t>https://artportalen.se/Sighting/132446055</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132397692</v>
+        <v>132446062</v>
       </c>
       <c r="B22" t="n">
-        <v>96261</v>
+        <v>96501</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2857,37 +2872,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2676</v>
+        <v>2671</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>348539</v>
+        <v>348457</v>
       </c>
       <c r="R22" t="n">
-        <v>6519214</v>
+        <v>6519522</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2911,12 +2926,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2927,36 +2942,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132397692</t>
+          <t>https://artportalen.se/Sighting/132446062</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132446060</v>
+        <v>136097925</v>
       </c>
       <c r="B23" t="n">
-        <v>96261</v>
+        <v>96596</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2964,34 +2974,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2676</v>
+        <v>2671</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>348457</v>
+        <v>348567</v>
       </c>
       <c r="R23" t="n">
-        <v>6519520</v>
+        <v>6519639</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3018,12 +3028,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,16 +3059,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446060</t>
+          <t>https://artportalen.se/Sighting/136097925</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132335999</v>
+        <v>132397692</v>
       </c>
       <c r="B24" t="n">
-        <v>96306</v>
+        <v>96261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3066,21 +3076,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2779</v>
+        <v>2676</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3156,16 +3166,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335999</t>
+          <t>https://artportalen.se/Sighting/132397692</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132446045</v>
+        <v>132446060</v>
       </c>
       <c r="B25" t="n">
-        <v>96306</v>
+        <v>96261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,34 +3183,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2779</v>
+        <v>2676</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>348545</v>
+        <v>348457</v>
       </c>
       <c r="R25" t="n">
-        <v>6519237</v>
+        <v>6519520</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3258,13 +3268,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446045</t>
+          <t>https://artportalen.se/Sighting/132446060</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132446059</v>
+        <v>132335999</v>
       </c>
       <c r="B26" t="n">
         <v>96306</v>
@@ -3295,17 +3305,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>348464</v>
+        <v>348539</v>
       </c>
       <c r="R26" t="n">
-        <v>6519521</v>
+        <v>6519214</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3329,12 +3339,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,31 +3355,36 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446059</t>
+          <t>https://artportalen.se/Sighting/132335999</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132335439</v>
+        <v>132446045</v>
       </c>
       <c r="B27" t="n">
-        <v>96533</v>
+        <v>96306</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3377,37 +3392,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>348505</v>
+        <v>348545</v>
       </c>
       <c r="R27" t="n">
-        <v>6519139</v>
+        <v>6519237</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3431,12 +3446,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3447,41 +3462,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Grov, murken granlåga.</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335439</t>
+          <t>https://artportalen.se/Sighting/132446045</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132335525</v>
+        <v>132446059</v>
       </c>
       <c r="B28" t="n">
-        <v>57972</v>
+        <v>96306</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3489,49 +3494,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>2779</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>348462</v>
+        <v>348464</v>
       </c>
       <c r="R28" t="n">
-        <v>6519162</v>
+        <v>6519521</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3555,12 +3548,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3575,27 +3568,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335525</t>
+          <t>https://artportalen.se/Sighting/132446059</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132446065</v>
+        <v>132335439</v>
       </c>
       <c r="B29" t="n">
-        <v>4776</v>
+        <v>96533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,42 +3596,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100299</v>
+        <v>2818</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>348443</v>
+        <v>348505</v>
       </c>
       <c r="R29" t="n">
-        <v>6519628</v>
+        <v>6519139</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3662,12 +3650,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3679,45 +3667,40 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Grov, murken granlåga.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446065</t>
+          <t>https://artportalen.se/Sighting/132335439</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132446063</v>
+        <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>5201</v>
+        <v>96628</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3725,39 +3708,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>105930</v>
+        <v>2818</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>348439</v>
+        <v>348719</v>
       </c>
       <c r="R30" t="n">
-        <v>6519636</v>
+        <v>6519093</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3784,12 +3762,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3830,16 +3808,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446063</t>
+          <t>https://artportalen.se/Sighting/136097899</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132446064</v>
+        <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>5201</v>
+        <v>96628</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3847,39 +3825,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>105930</v>
+        <v>2818</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>348443</v>
+        <v>348560</v>
       </c>
       <c r="R31" t="n">
-        <v>6519628</v>
+        <v>6519339</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3906,12 +3879,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3952,16 +3925,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446064</t>
+          <t>https://artportalen.se/Sighting/136097906</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132446066</v>
+        <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>5201</v>
+        <v>96628</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3969,39 +3942,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>105930</v>
+        <v>2818</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>348507</v>
+        <v>348545</v>
       </c>
       <c r="R32" t="n">
-        <v>6519811</v>
+        <v>6519374</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4028,12 +3996,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4074,59 +4042,66 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446066</t>
+          <t>https://artportalen.se/Sighting/136097907</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132446029</v>
+        <v>132335525</v>
       </c>
       <c r="B33" t="n">
-        <v>8374</v>
+        <v>57972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106540</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Dls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>348623</v>
+        <v>348462</v>
       </c>
       <c r="R33" t="n">
-        <v>6519241</v>
+        <v>6519162</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4150,12 +4125,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4166,46 +4141,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446029</t>
+          <t>https://artportalen.se/Sighting/132335525</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132446056</v>
+        <v>132446065</v>
       </c>
       <c r="B34" t="n">
-        <v>8460</v>
+        <v>4776</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4213,27 +4173,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4242,10 +4202,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>348430</v>
+        <v>348443</v>
       </c>
       <c r="R34" t="n">
-        <v>6519483</v>
+        <v>6519628</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4291,17 +4251,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4318,51 +4278,56 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446056</t>
+          <t>https://artportalen.se/Sighting/132446065</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132446053</v>
+        <v>132446063</v>
       </c>
       <c r="B35" t="n">
-        <v>111471</v>
+        <v>5201</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219711</v>
+        <v>105930</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>348463</v>
+        <v>348439</v>
       </c>
       <c r="R35" t="n">
-        <v>6519366</v>
+        <v>6519636</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4406,6 +4371,21 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
@@ -4420,16 +4400,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446053</t>
+          <t>https://artportalen.se/Sighting/132446063</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121791871</v>
+        <v>132446064</v>
       </c>
       <c r="B36" t="n">
-        <v>101326</v>
+        <v>5201</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4437,47 +4417,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>348561</v>
+        <v>348443</v>
       </c>
       <c r="R36" t="n">
-        <v>6519216</v>
+        <v>6519628</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4501,12 +4476,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4518,35 +4493,45 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121791871</t>
+          <t>https://artportalen.se/Sighting/132446064</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121792063</v>
+        <v>132446066</v>
       </c>
       <c r="B37" t="n">
-        <v>101326</v>
+        <v>5201</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4554,47 +4539,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>348553</v>
+        <v>348507</v>
       </c>
       <c r="R37" t="n">
-        <v>6519199</v>
+        <v>6519811</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4618,12 +4598,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4635,83 +4615,88 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792063</t>
+          <t>https://artportalen.se/Sighting/132446066</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121792253</v>
+        <v>132446029</v>
       </c>
       <c r="B38" t="n">
-        <v>101326</v>
+        <v>8374</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>106540</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>348514</v>
+        <v>348623</v>
       </c>
       <c r="R38" t="n">
-        <v>6519160</v>
+        <v>6519241</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4735,12 +4720,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4752,35 +4737,45 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792253</t>
+          <t>https://artportalen.se/Sighting/132446029</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121792318</v>
+        <v>132446056</v>
       </c>
       <c r="B39" t="n">
-        <v>101326</v>
+        <v>8460</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4788,47 +4783,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>348459</v>
+        <v>348430</v>
       </c>
       <c r="R39" t="n">
-        <v>6519139</v>
+        <v>6519483</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4852,12 +4842,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4869,83 +4859,83 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792318</t>
+          <t>https://artportalen.se/Sighting/132446056</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121792399</v>
+        <v>132446053</v>
       </c>
       <c r="B40" t="n">
-        <v>101326</v>
+        <v>111471</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>348481</v>
+        <v>348463</v>
       </c>
       <c r="R40" t="n">
-        <v>6519252</v>
+        <v>6519366</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4969,12 +4959,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4985,84 +4975,69 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792399</t>
+          <t>https://artportalen.se/Sighting/132446053</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121792568</v>
+        <v>136097900</v>
       </c>
       <c r="B41" t="n">
-        <v>101326</v>
+        <v>111586</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>348486</v>
+        <v>348618</v>
       </c>
       <c r="R41" t="n">
-        <v>6519336</v>
+        <v>6519260</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5086,12 +5061,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5102,33 +5077,28 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792568</t>
+          <t>https://artportalen.se/Sighting/136097900</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121792607</v>
+        <v>121791871</v>
       </c>
       <c r="B42" t="n">
         <v>101326</v>
@@ -5169,14 +5139,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>348455</v>
+        <v>348561</v>
       </c>
       <c r="R42" t="n">
-        <v>6519346</v>
+        <v>6519216</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5222,7 +5192,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5239,16 +5209,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792607</t>
+          <t>https://artportalen.se/Sighting/121791871</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132335808</v>
+        <v>121792063</v>
       </c>
       <c r="B43" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5274,16 +5244,26 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>348481</v>
+        <v>348553</v>
       </c>
       <c r="R43" t="n">
-        <v>6519286</v>
+        <v>6519199</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5310,12 +5290,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5326,31 +5306,36 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335808</t>
+          <t>https://artportalen.se/Sighting/121792063</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132336006</v>
+        <v>121792253</v>
       </c>
       <c r="B44" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5376,16 +5361,26 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>348550</v>
+        <v>348514</v>
       </c>
       <c r="R44" t="n">
-        <v>6519223</v>
+        <v>6519160</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5412,12 +5407,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5429,35 +5424,35 @@
       <c r="AG44" t="b">
         <v>0</v>
       </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336006</t>
+          <t>https://artportalen.se/Sighting/121792253</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132336196</v>
+        <v>121792318</v>
       </c>
       <c r="B45" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5483,16 +5478,26 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>348529</v>
+        <v>348459</v>
       </c>
       <c r="R45" t="n">
-        <v>6519171</v>
+        <v>6519139</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5519,12 +5524,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5536,35 +5541,35 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336196</t>
+          <t>https://artportalen.se/Sighting/121792318</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132336478</v>
+        <v>121792399</v>
       </c>
       <c r="B46" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5590,16 +5595,26 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>348493</v>
+        <v>348481</v>
       </c>
       <c r="R46" t="n">
-        <v>6519126</v>
+        <v>6519252</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5626,12 +5641,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5642,31 +5657,36 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336478</t>
+          <t>https://artportalen.se/Sighting/121792399</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132446046</v>
+        <v>121792568</v>
       </c>
       <c r="B47" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5692,19 +5712,29 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>348506</v>
+        <v>348486</v>
       </c>
       <c r="R47" t="n">
-        <v>6519266</v>
+        <v>6519336</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5728,12 +5758,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5744,31 +5774,36 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446046</t>
+          <t>https://artportalen.se/Sighting/121792568</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132446050</v>
+        <v>121792607</v>
       </c>
       <c r="B48" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5794,19 +5829,29 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>348486</v>
+        <v>348455</v>
       </c>
       <c r="R48" t="n">
-        <v>6519319</v>
+        <v>6519346</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5830,12 +5875,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5846,28 +5891,33 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446050</t>
+          <t>https://artportalen.se/Sighting/121792607</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132446052</v>
+        <v>132335808</v>
       </c>
       <c r="B49" t="n">
         <v>101403</v>
@@ -5898,17 +5948,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>348480</v>
+        <v>348481</v>
       </c>
       <c r="R49" t="n">
-        <v>6519355</v>
+        <v>6519286</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5932,12 +5982,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5952,27 +6002,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446052</t>
+          <t>https://artportalen.se/Sighting/132335808</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132336005</v>
+        <v>132336006</v>
       </c>
       <c r="B50" t="n">
-        <v>101324</v>
+        <v>101403</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5980,21 +6030,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222782</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitsippa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anemone nemorosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6070,16 +6120,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336005</t>
+          <t>https://artportalen.se/Sighting/132336006</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132446061</v>
+        <v>132336196</v>
       </c>
       <c r="B51" t="n">
-        <v>80403</v>
+        <v>101403</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6087,37 +6137,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6003719</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>348457</v>
+        <v>348529</v>
       </c>
       <c r="R51" t="n">
-        <v>6519520</v>
+        <v>6519171</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6141,12 +6191,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6157,20 +6207,642 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336196</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132336478</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>348493</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6519126</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336478</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>132446046</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>348506</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6519266</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446046</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132446050</v>
+      </c>
+      <c r="B54" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>348486</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6519319</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446050</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132446052</v>
+      </c>
+      <c r="B55" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>348480</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6519355</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446052</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>132336005</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>348550</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6519223</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336005</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132446061</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80403</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skog väster om Lilla Skårsdalstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>348457</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6519520</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132446061</t>
         </is>
@@ -6228,6 +6900,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2023,7 +2023,7 @@
         <v>136097908</v>
       </c>
       <c r="B14" t="n">
-        <v>96607</v>
+        <v>96608</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136097925</v>
       </c>
       <c r="B23" t="n">
-        <v>96596</v>
+        <v>96597</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96628</v>
+        <v>96629</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96628</v>
+        <v>96629</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96628</v>
+        <v>96629</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>136097900</v>
       </c>
       <c r="B41" t="n">
-        <v>111586</v>
+        <v>111588</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2023,7 +2023,7 @@
         <v>136097908</v>
       </c>
       <c r="B14" t="n">
-        <v>96608</v>
+        <v>96609</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136097925</v>
       </c>
       <c r="B23" t="n">
-        <v>96597</v>
+        <v>96598</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96629</v>
+        <v>96630</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96629</v>
+        <v>96630</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96629</v>
+        <v>96630</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>136097900</v>
       </c>
       <c r="B41" t="n">
-        <v>111588</v>
+        <v>111589</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2023,7 +2023,7 @@
         <v>136097908</v>
       </c>
       <c r="B14" t="n">
-        <v>96609</v>
+        <v>96610</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136097925</v>
       </c>
       <c r="B23" t="n">
-        <v>96598</v>
+        <v>96599</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>136097900</v>
       </c>
       <c r="B41" t="n">
-        <v>111589</v>
+        <v>111590</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2023,7 +2023,7 @@
         <v>136097908</v>
       </c>
       <c r="B14" t="n">
-        <v>96610</v>
+        <v>96616</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136097925</v>
       </c>
       <c r="B23" t="n">
-        <v>96599</v>
+        <v>96605</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96631</v>
+        <v>96637</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96631</v>
+        <v>96637</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96631</v>
+        <v>96637</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>136097900</v>
       </c>
       <c r="B41" t="n">
-        <v>111590</v>
+        <v>111596</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2023,7 +2023,7 @@
         <v>136097908</v>
       </c>
       <c r="B14" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136097925</v>
       </c>
       <c r="B23" t="n">
-        <v>96605</v>
+        <v>96606</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96637</v>
+        <v>96638</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96637</v>
+        <v>96638</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96637</v>
+        <v>96638</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>136097900</v>
       </c>
       <c r="B41" t="n">
-        <v>111596</v>
+        <v>111597</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2023,7 +2023,7 @@
         <v>136097908</v>
       </c>
       <c r="B14" t="n">
-        <v>96617</v>
+        <v>96628</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136097925</v>
       </c>
       <c r="B23" t="n">
-        <v>96606</v>
+        <v>96617</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96638</v>
+        <v>96649</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96638</v>
+        <v>96649</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96638</v>
+        <v>96649</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>136097900</v>
       </c>
       <c r="B41" t="n">
-        <v>111597</v>
+        <v>111608</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2023,7 +2023,7 @@
         <v>136097908</v>
       </c>
       <c r="B14" t="n">
-        <v>96628</v>
+        <v>96641</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136097925</v>
       </c>
       <c r="B23" t="n">
-        <v>96617</v>
+        <v>96630</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96649</v>
+        <v>96662</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96649</v>
+        <v>96662</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96649</v>
+        <v>96662</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>136097900</v>
       </c>
       <c r="B41" t="n">
-        <v>111608</v>
+        <v>111621</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2023,7 +2023,7 @@
         <v>136097908</v>
       </c>
       <c r="B14" t="n">
-        <v>96641</v>
+        <v>96642</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136097925</v>
       </c>
       <c r="B23" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96662</v>
+        <v>96663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96662</v>
+        <v>96663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96662</v>
+        <v>96663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>136097900</v>
       </c>
       <c r="B41" t="n">
-        <v>111621</v>
+        <v>111622</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2023,7 +2023,7 @@
         <v>136097908</v>
       </c>
       <c r="B14" t="n">
-        <v>96642</v>
+        <v>96655</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136097925</v>
       </c>
       <c r="B23" t="n">
-        <v>96631</v>
+        <v>96644</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96663</v>
+        <v>96676</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96663</v>
+        <v>96676</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96663</v>
+        <v>96676</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>136097900</v>
       </c>
       <c r="B41" t="n">
-        <v>111622</v>
+        <v>111635</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 16664-2026 artfynd.xlsx
+++ b/artfynd/A 16664-2026 artfynd.xlsx
@@ -2023,7 +2023,7 @@
         <v>136097908</v>
       </c>
       <c r="B14" t="n">
-        <v>96655</v>
+        <v>96656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136097925</v>
       </c>
       <c r="B23" t="n">
-        <v>96644</v>
+        <v>96645</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96676</v>
+        <v>96677</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96676</v>
+        <v>96677</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96676</v>
+        <v>96677</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>136097900</v>
       </c>
       <c r="B41" t="n">
-        <v>111635</v>
+        <v>111636</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
